--- a/backend/data/DSA1101_Sem1_2425_Quiz4.xlsx
+++ b/backend/data/DSA1101_Sem1_2425_Quiz4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/extracted_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/dsa3101-2510-quiz-02/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFD21C0-3817-F346-8443-E942BB60B255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9176FF92-2BA9-3447-A934-F079C5B73733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16660" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
   </bookViews>
@@ -39,9 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
-    <t>Context ID</t>
-  </si>
-  <si>
     <t>Context Text</t>
   </si>
   <si>
@@ -216,6 +213,9 @@
   </si>
   <si>
     <t>Sub-Question Number</t>
+  </si>
+  <si>
+    <t>Context ID</t>
   </si>
 </sst>
 </file>
@@ -604,14 +604,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="85" x14ac:dyDescent="0.2">
@@ -619,10 +619,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="68" x14ac:dyDescent="0.2">
@@ -630,10 +630,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -654,53 +654,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
       <c r="P1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -711,28 +711,28 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="N2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" t="s">
         <v>43</v>
-      </c>
-      <c r="O2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -743,31 +743,31 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
       <c r="N3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -778,31 +778,31 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>31</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="N4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -813,22 +813,22 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
         <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
       </c>
       <c r="K5">
         <v>1250</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -839,10 +839,10 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -851,13 +851,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O6" t="s">
         <v>43</v>
-      </c>
-      <c r="O6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="221" x14ac:dyDescent="0.2">
@@ -868,10 +868,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -880,16 +880,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="153" x14ac:dyDescent="0.2">
@@ -900,10 +900,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -912,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" t="s">
         <v>42</v>
       </c>
-      <c r="N8" t="s">
-        <v>43</v>
-      </c>
       <c r="O8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
